--- a/rfq/IOB_RFQ_to_DSR_-_Mooring_Tail.xlsx
+++ b/rfq/IOB_RFQ_to_DSR_-_Mooring_Tail.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
   <si>
     <t xml:space="preserve">REQUEST FOR QUOTATION</t>
   </si>
@@ -143,28 +143,10 @@
     <t xml:space="preserve">AEOLUS</t>
   </si>
   <si>
-    <t xml:space="preserve">Mooring tail Ø104 mm x 11 m
-Nylon 8-strand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSR, NYLON TAIL ROPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ref. Cert. UMC1154-39
-(Order UD1039, Hanwha Ocean H2525, 2024-11-27)</t>
+    <t xml:space="preserve">Mooring tail rope (Nylon), 11 m</t>
   </si>
   <si>
     <t xml:space="preserve">Mooring tail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Material: Nylon multifilament (polyamide)
-Construction: 8 strand, non-rotating, not jacketed
-Diameter 104 mm  /  Length 11 m
-Ship design MBL: 125 TON
-Splice: DSR spliced method
-Mfd. to ISO 9554:2010 &amp; ISO 1140:2021
-Wet-tested to OCIMF MEG4 App. B / ISO 2307 / CI 1500
-MEG4 mooring tail certificate to be supplied</t>
   </si>
   <si>
     <t xml:space="preserve">PCS</t>
@@ -1021,7 +1003,7 @@
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
     </row>
-    <row r="14" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="n">
         <v>1</v>
       </c>
@@ -1031,23 +1013,17 @@
       <c r="C14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>43</v>
-      </c>
+      <c r="G14" s="11"/>
       <c r="H14" s="9" t="n">
         <v>14</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J14" s="12"/>
       <c r="K14" s="13" t="str">
@@ -1058,33 +1034,27 @@
       <c r="M14" s="14"/>
       <c r="N14" s="15"/>
     </row>
-    <row r="15" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="n">
         <v>2</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>43</v>
-      </c>
+      <c r="G15" s="11"/>
       <c r="H15" s="9" t="n">
         <v>16</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J15" s="12"/>
       <c r="K15" s="13" t="str">
@@ -1095,33 +1065,27 @@
       <c r="M15" s="14"/>
       <c r="N15" s="15"/>
     </row>
-    <row r="16" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="n">
         <v>3</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>43</v>
-      </c>
+      <c r="G16" s="11"/>
       <c r="H16" s="9" t="n">
         <v>22</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="13" t="str">
@@ -1159,7 +1123,7 @@
       <c r="H18" s="16"/>
       <c r="I18" s="16"/>
       <c r="J18" s="17" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K18" s="18" t="n">
         <f aca="false">SUM(K14:K16)</f>
@@ -1187,12 +1151,12 @@
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1222,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1266,16 +1230,16 @@
         <v>24</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1283,13 +1247,13 @@
         <v>38</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E4" s="23" t="n">
         <f aca="false">COUNTIF(RFQ!$B$14:$B$16,A4)</f>
@@ -1298,16 +1262,16 @@
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E5" s="23" t="n">
         <f aca="false">COUNTIF(RFQ!$B$14:$B$16,A5)</f>
@@ -1316,16 +1280,16 @@
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B6" s="23" t="n">
         <v>9958303</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E6" s="23" t="n">
         <f aca="false">COUNTIF(RFQ!$B$14:$B$16,A6)</f>
@@ -1334,7 +1298,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
